--- a/tests/testdata/excels/valid/InlineStrings.xlsx
+++ b/tests/testdata/excels/valid/InlineStrings.xlsx
@@ -17,7 +17,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>*id</t>
+          <t>id#</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
